--- a/HotGuy/Assets/Config/Excel/DanmakuPoolConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/DanmakuPoolConfig.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BC9F90-58EF-4C36-AE56-6F767703A06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1073" yWindow="1073" windowWidth="14400" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1234" yWindow="1226" windowWidth="14383" windowHeight="9831" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodConfig" sheetId="1" r:id="rId1"/>
